--- a/public/files/Data_By_Towns_Index/Camden/Camden City.xlsx
+++ b/public/files/Data_By_Towns_Index/Camden/Camden City.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,478 +425,201 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Unnamed: 0</t>
+          <t>Owner Name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Owner Name</t>
+          <t>Property Location</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Property Location</t>
+          <t>Municipality</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Municipality</t>
+          <t>County</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>State</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Longitude</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>PID</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PATEL, ANIL</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DESAI, ASHOK</t>
+          <t>2732 HAYES AVE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1361 DAYTON ST</t>
+          <t>Camden City</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Camden City</t>
+          <t>Camden</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Desai</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>39.9225843</v>
+        <v>-75.0918942</v>
       </c>
       <c r="G2" t="n">
-        <v>-75.0993369</v>
+        <v>39.9550069</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ChIJbaI5IKTJxokRbq0HtR61JE8</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SHARMA, MARIA</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GUPTA, VISHNU</t>
+          <t>20 SO 35TH ST</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>700 NEW ST UNIT 105</t>
+          <t>Camden City</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Camden City</t>
+          <t>Camden</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gupta</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>39.9392328</v>
+        <v>-75.07318289999999</v>
       </c>
       <c r="G3" t="n">
-        <v>-75.1157915</v>
+        <v>39.9471536</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ChIJK9YN_HfJxokR8-BRl45sPtc</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PATEL, TINESHA D</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PATEL, ANIL</t>
+          <t>1587 GREENWOOD AVE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2732 HAYES AVE</t>
+          <t>Camden City</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Camden City</t>
+          <t>Camden</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>39.9550069</v>
+        <v>-75.09345069999999</v>
       </c>
       <c r="G4" t="n">
-        <v>-75.0918942</v>
+        <v>39.9288602</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ChIJeacGdT3JxokRaS-fMhy5tco</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PATEL, RAKESH</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PATEL, KIRAN</t>
+          <t>315 POINT ST</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3121 WESTFIELD AVE</t>
+          <t>Camden City</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Camden City</t>
+          <t>Camden</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>39.9496177</v>
+        <v>-75.12653060000001</v>
       </c>
       <c r="G5" t="n">
-        <v>-75.0808485</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>PATEL, RAKESH</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>315 POINT ST</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Camden City</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
         <v>39.9495194</v>
       </c>
-      <c r="G6" t="n">
-        <v>-75.12653060000001</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>PATEL, TINESHA D</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1587 GREENWOOD AVE</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Camden City</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>39.9288602</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-75.09345069999999</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>SHAH, SYED M</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>4545 CRESCENT BLVD</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Camden City</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Shah</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>39.9017888</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-75.09812549999999</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>SHAH, SYED M</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>4545 CRESCENT BLVD</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Camden City</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Shah</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>39.9017888</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-75.09812549999999</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>SHAH, SYED M</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>4545 CRESCENT BLVD</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Camden City</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Shah</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>39.9017888</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-75.09812549999999</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>SHARMA, MARIA</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>20 SO 35TH ST</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Camden City</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Sharma</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>39.9471536</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-75.07318289999999</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>AMIN, KAHLID</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1188 KAIGHN AVE</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Camden City</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Amin</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>39.9317348</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-75.10514259999999</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>AMIN, KHALID</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1312 MT EPHRAIM AVE</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Camden City</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Amin</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>39.9305853</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-75.1079587</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>AMIN, KHALID</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>486 RAND ST</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Camden City</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Amin</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>39.9401103</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-75.0864634</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>DALAL, SHRIDATT</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2213 RIVER AVE</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Camden City</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Dalal</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>39.9531844</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-75.09688269999999</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ChIJj1-zC_TIxokRYRpXyQ0MYK0</t>
+        </is>
       </c>
     </row>
   </sheetData>
